--- a/docs/reference-forms/output/xlsx/TAI-FORM-REF-C009.xlsx
+++ b/docs/reference-forms/output/xlsx/TAI-FORM-REF-C009.xlsx
@@ -10,8 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안전보건 전문인력 등 배치표 및 담당업무" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'안전보건 전문인력 등 배치표 및 담당업무'!$A$2:$D$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'안전보건 전문인력 등 배치표 및 담당업무'!$A$1:$D$46</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'안전보건 전문인력 등 배치표 및 담당업무'!$A$1:$D$301</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -186,6 +185,19 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_REF_C009_1" displayName="T_REF_C009_1" ref="A2:D62" headerRowCount="1">
+  <autoFilter ref="A2:D62"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="직책"/>
+    <tableColumn id="2" name="성명"/>
+    <tableColumn id="3" name="담당업무"/>
+    <tableColumn id="4" name="비고"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -477,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.6" customWidth="1" min="1" max="1"/>
@@ -551,316 +563,642 @@
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr"/>
     </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="3" t="inlineStr"/>
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="3" t="inlineStr"/>
+      <c r="B10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="3" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="3" t="inlineStr"/>
+      <c r="B12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr"/>
+      <c r="D12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="3" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr"/>
+      <c r="D14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="3" t="inlineStr"/>
+      <c r="B15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="3" t="inlineStr"/>
+      <c r="B16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="inlineStr"/>
+      <c r="D16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="3" t="inlineStr"/>
+      <c r="B17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="3" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="3" t="inlineStr"/>
+      <c r="B19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="3" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="3" t="inlineStr"/>
+      <c r="B21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="3" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="inlineStr"/>
+      <c r="D22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="3" t="inlineStr"/>
+      <c r="B23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="3" t="inlineStr"/>
+      <c r="B24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="inlineStr"/>
+      <c r="D24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="3" t="inlineStr"/>
+      <c r="B25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="3" t="inlineStr"/>
+      <c r="B26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="inlineStr"/>
+      <c r="D26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="3" t="inlineStr"/>
+      <c r="B27" s="3" t="inlineStr"/>
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="3" t="inlineStr"/>
+      <c r="B28" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="inlineStr"/>
+      <c r="D28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="3" t="inlineStr"/>
+      <c r="B29" s="3" t="inlineStr"/>
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="3" t="inlineStr"/>
+      <c r="B30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="3" t="inlineStr"/>
+      <c r="B31" s="3" t="inlineStr"/>
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="3" t="inlineStr"/>
+      <c r="B32" s="3" t="inlineStr"/>
+      <c r="C32" s="3" t="inlineStr"/>
+      <c r="D32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="3" t="inlineStr"/>
+      <c r="B33" s="3" t="inlineStr"/>
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="3" t="inlineStr"/>
+      <c r="B34" s="3" t="inlineStr"/>
+      <c r="C34" s="3" t="inlineStr"/>
+      <c r="D34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="3" t="inlineStr"/>
+      <c r="B35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="3" t="inlineStr"/>
+      <c r="B36" s="3" t="inlineStr"/>
+      <c r="C36" s="3" t="inlineStr"/>
+      <c r="D36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="3" t="inlineStr"/>
+      <c r="B37" s="3" t="inlineStr"/>
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="3" t="inlineStr"/>
+      <c r="B38" s="3" t="inlineStr"/>
+      <c r="C38" s="3" t="inlineStr"/>
+      <c r="D38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="3" t="inlineStr"/>
+      <c r="B39" s="3" t="inlineStr"/>
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="3" t="inlineStr"/>
+      <c r="B40" s="3" t="inlineStr"/>
+      <c r="C40" s="3" t="inlineStr"/>
+      <c r="D40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="3" t="inlineStr"/>
+      <c r="B41" s="3" t="inlineStr"/>
+      <c r="C41" s="3" t="inlineStr"/>
+      <c r="D41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="3" t="inlineStr"/>
+      <c r="B42" s="3" t="inlineStr"/>
+      <c r="C42" s="3" t="inlineStr"/>
+      <c r="D42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="3" t="inlineStr"/>
+      <c r="B43" s="3" t="inlineStr"/>
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="3" t="inlineStr"/>
+      <c r="B44" s="3" t="inlineStr"/>
+      <c r="C44" s="3" t="inlineStr"/>
+      <c r="D44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="3" t="inlineStr"/>
+      <c r="B45" s="3" t="inlineStr"/>
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="3" t="inlineStr"/>
+      <c r="B46" s="3" t="inlineStr"/>
+      <c r="C46" s="3" t="inlineStr"/>
+      <c r="D46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="3" t="inlineStr"/>
+      <c r="B47" s="3" t="inlineStr"/>
+      <c r="C47" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="3" t="inlineStr"/>
+      <c r="B48" s="3" t="inlineStr"/>
+      <c r="C48" s="3" t="inlineStr"/>
+      <c r="D48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="3" t="inlineStr"/>
+      <c r="B49" s="3" t="inlineStr"/>
+      <c r="C49" s="3" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="3" t="inlineStr"/>
+      <c r="B50" s="3" t="inlineStr"/>
+      <c r="C50" s="3" t="inlineStr"/>
+      <c r="D50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="3" t="inlineStr"/>
+      <c r="B51" s="3" t="inlineStr"/>
+      <c r="C51" s="3" t="inlineStr"/>
+      <c r="D51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="3" t="inlineStr"/>
+      <c r="B52" s="3" t="inlineStr"/>
+      <c r="C52" s="3" t="inlineStr"/>
+      <c r="D52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="3" t="inlineStr"/>
+      <c r="B53" s="3" t="inlineStr"/>
+      <c r="C53" s="3" t="inlineStr"/>
+      <c r="D53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="3" t="inlineStr"/>
+      <c r="B54" s="3" t="inlineStr"/>
+      <c r="C54" s="3" t="inlineStr"/>
+      <c r="D54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="3" t="inlineStr"/>
+      <c r="B55" s="3" t="inlineStr"/>
+      <c r="C55" s="3" t="inlineStr"/>
+      <c r="D55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="3" t="inlineStr"/>
+      <c r="B56" s="3" t="inlineStr"/>
+      <c r="C56" s="3" t="inlineStr"/>
+      <c r="D56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="3" t="inlineStr"/>
+      <c r="B57" s="3" t="inlineStr"/>
+      <c r="C57" s="3" t="inlineStr"/>
+      <c r="D57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="3" t="inlineStr"/>
+      <c r="B58" s="3" t="inlineStr"/>
+      <c r="C58" s="3" t="inlineStr"/>
+      <c r="D58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="3" t="inlineStr"/>
+      <c r="B59" s="3" t="inlineStr"/>
+      <c r="C59" s="3" t="inlineStr"/>
+      <c r="D59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="3" t="inlineStr"/>
+      <c r="B60" s="3" t="inlineStr"/>
+      <c r="C60" s="3" t="inlineStr"/>
+      <c r="D60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="3" t="inlineStr"/>
+      <c r="B61" s="3" t="inlineStr"/>
+      <c r="C61" s="3" t="inlineStr"/>
+      <c r="D61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="3" t="inlineStr"/>
+      <c r="B62" s="3" t="inlineStr"/>
+      <c r="C62" s="3" t="inlineStr"/>
+      <c r="D62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>【직책별 담당업무 참조】 (산업안전보건법)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>안전관리자 (산안법 제17조)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="65" ht="28" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. 산업안전보건위원회 또는 안전·보건에 관한 노사협의체에서 심의·의결한 업무와 해당 사업장의 안전보건관리규정 및 취업규칙에서 정한 업무</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="66" ht="28" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. 위험성평가에 관한 보좌 및 지도·조언</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="67" ht="28" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. 안전인증대상기계등과 자율안전확인대상기계등 구입 시 적격품의 선정에 관한 보좌 및 지도·조언</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="68" ht="28" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. 해당 사업장 안전교육계획의 수립 및 안전교육 실시에 관한 보좌 및 지도·조언</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. 사업장 순회점검, 지도 및 조치 건의</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  6. 산업재해 발생의 원인조사·분석 및 재발방지를 위한 기술적 보좌 및 지도·조언</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="71" ht="28" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  7. 산업재해에 관한 통계의 유지·관리·분석을 위한 보좌 및 지도·조언</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="72" ht="28" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  8. 법 또는 법에 따른 명령으로 정한 안전에 관한 사항의 이행에 관한 보좌 및 지도·조언</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="73" ht="28" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  9. 업무수행 내용의 기록·유지</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="74" ht="28" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  10. 그 밖에 안전에 관한 사항으로서 고용노동부장관이 정하는 사항</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="75" ht="28" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>보건관리자 (산안법 제18조)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="76" ht="28" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. 산업안전보건위원회 또는 노사협의체에서 심의·의결한 업무와 안전보건관리규정 및 취업규칙에서 정한 업무</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="77" ht="28" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. 안전인증대상기계등과 자율안전확인대상기계등 중 보건과 관련된 보호구 구입 시 적격품 선정에 관한 보좌 및 지도·조언</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="78" ht="28" customHeight="1">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. 위험성평가에 관한 보좌 및 지도·조언</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="79" ht="28" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. 물질안전보건자료의 게시 또는 비치에 관한 보좌 및 지도·조언</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="80" ht="28" customHeight="1">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. 시행령 제31조제1항에 따른 산업보건의의 직무(보건관리자가 ｢의료법｣에 따른 의사인 경우에 한함)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="81" ht="28" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  6. 해당 사업장 보건교육계획의 수립 및 보건교육 실시에 관한 보좌 및 지도·조언</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="82" ht="28" customHeight="1">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  7. 해당 사업장의 근로자를 보호하기 위한 자주 발생하는 가벼운 부상에 대한 치료, 응급처치가 필요한 사람에 대한 처치, 부상·질병의 악화를 방지하기 위한 처치, 건강진단 결과 발견된 질병자의 요양지도 및 관리, 위 의료행위에 따르는 의약품의 투여에 해당하는 의료행위(보건관리자가 ｢의료법｣에 따른 의사 또는 간호사인 경우에 한함)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="83" ht="28" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  8. 작업장 내에서 사용되는 전체 환기장치 및 국소 배기장치 등에 관한 설비의 점검과 작업방법의 공학적 개선에 관한 보좌 및 지도·조언</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="84" ht="28" customHeight="1">
+      <c r="A84" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  9. 사업장 순회점검·지도 및 조치의 건의</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="85" ht="28" customHeight="1">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  10. 산업재해 발생의 원인조사·분석 및 재발 방지를 위한 기술적 보좌 및 지도·조언</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="86" ht="28" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  11. 산업재해 통계의 유지·관리·분석을 위한 보좌 및 지도·조언</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="87" ht="28" customHeight="1">
+      <c r="A87" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  12. 법 또는 법에 따른 명령으로 정한 보건에 관한 사항의 이행에 관한 보좌 및 지도·조언</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="88" ht="28" customHeight="1">
+      <c r="A88" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  13. 업무수행 내용의 기록·유지</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="89" ht="28" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  14. 그 밖에 보건과 관련된 작업관리 및 작업환경관리에 관한 사항</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="90" ht="28" customHeight="1">
+      <c r="A90" s="4" t="inlineStr">
         <is>
           <t>안전보건관리담당자 (산안법 제19조)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="91" ht="28" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. 안전보건교육 실시에 관한 보좌 및 지도·조언</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
+    <row r="92" ht="28" customHeight="1">
+      <c r="A92" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. 위험성평가에 관한 보좌 및 지도·조언</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="93" ht="28" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. 작업환경측정 및 개선에 관한 보좌 및 지도·조언</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
+    <row r="94" ht="28" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. 건강진단에 관한 보좌 및 지도·조언</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="95" ht="28" customHeight="1">
+      <c r="A95" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. 산업재해 발생의 원인조사, 산업재해 통계의 기록 및 유지를 위한 보좌 및 지도·조언</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
+    <row r="96" ht="28" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  6. 산업안전·보건과 관련된 안전장치 및 보호구 구입 시 적격품 선정에 관한 보좌 및 지도·조언</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="97" ht="28" customHeight="1">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t>산업보건의 (산안법 제22조)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
+    <row r="98" ht="28" customHeight="1">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. 건강진단 결과의 검토 및 그 결과에 따른 작업 배치, 작업 전환 또는 근로시간의 단축 등 근로자의 건강보호 조치</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
+    <row r="99" ht="28" customHeight="1">
+      <c r="A99" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. 근로자의 건강장해의 원인 조사와 재발 방지를 위한 의학적 조치</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="4" t="inlineStr">
+    <row r="100" ht="28" customHeight="1">
+      <c r="A100" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. 그 밖에 근로자의 건강 유지 및 증진을 위하여 필요한 의학적 조치에 관하여 고용노동부장관이 정하는 사항</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D8"/>
   <mergeCells count="39">
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A91:D91"/>
+    <mergeCell ref="A97:D97"/>
+    <mergeCell ref="A100:D100"/>
+    <mergeCell ref="A96:D96"/>
+    <mergeCell ref="A72:D72"/>
+    <mergeCell ref="A81:D81"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A93:D93"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="A77:D77"/>
+    <mergeCell ref="A83:D83"/>
+    <mergeCell ref="A92:D92"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A82:D82"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A98:D98"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A94:D94"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A79:D79"/>
+    <mergeCell ref="A88:D88"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A78:D78"/>
+    <mergeCell ref="A87:D87"/>
+    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="A99:D99"/>
+    <mergeCell ref="A84:D84"/>
+    <mergeCell ref="A90:D90"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A80:D80"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="A89:D89"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A86:D86"/>
+    <mergeCell ref="A95:D95"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A85:D85"/>
+    <mergeCell ref="A76:D76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/docs/reference-forms/output/xlsx/TAI-FORM-REF-C009.xlsx
+++ b/docs/reference-forms/output/xlsx/TAI-FORM-REF-C009.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안전보건 전문인력 등 배치표 및 담당업무" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'안전보건 전문인력 등 배치표 및 담당업무'!$A$1:$D$301</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'안전보건 전문인력 등 배치표 및 담당업무'!$A$1:$D$100</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
